--- a/artfynd/A 38411-2022 artfynd.xlsx
+++ b/artfynd/A 38411-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38411-2022 artfynd.xlsx
+++ b/artfynd/A 38411-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>71504781</v>
       </c>
       <c r="B2" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376257.0224493146</v>
+        <v>376257</v>
       </c>
       <c r="R2" t="n">
-        <v>6285925.26934229</v>
+        <v>6285925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +745,9 @@
           <t>2018-05-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-05-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71504787</v>
+        <v>71504789</v>
       </c>
       <c r="B3" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,49 +790,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skedala skog, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376220.2400247815</v>
+        <v>376220</v>
       </c>
       <c r="R3" t="n">
-        <v>6285891.198775841</v>
+        <v>6285891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +854,9 @@
           <t>2018-05-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-05-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,11 +868,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lövträd</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -919,10 +876,127 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Viveka Strand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>71504787</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skedala skog, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>376220</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6285891</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-05-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-05-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lövträd</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Viveka Strand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Viveka Strand, Lars-Åke Flodin</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38411-2022 artfynd.xlsx
+++ b/artfynd/A 38411-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71504781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71504789</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71504787</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>